--- a/public/donnees-geographiques.xlsx
+++ b/public/donnees-geographiques.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hiérarchie Géographique" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Audit &amp; Suppression Supabase" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Synthèse Statistique" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Modèles de Codes Postaux" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guide des Structures Postales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,15 +87,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,15 +455,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,12 +490,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Code Postal</t>
+          <t>Modèle / Plage de Code Postal</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Identifiant Unique</t>
+          <t>Règle / Structure de Formatage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Exemples Types Représentatifs</t>
         </is>
       </c>
     </row>
@@ -527,14 +525,19 @@
           <t>1er Arrondissement (Louvre)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>75001</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>e1-fr-par-1</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 75001 à 75020 (750XX)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 750 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>75001 (Louvre), 75002 (Bourse), 75004 (Marais)</t>
         </is>
       </c>
     </row>
@@ -556,17 +559,22 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>8e Arrondissement (Élysée)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>75008</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>e2-fr-par-8</t>
+          <t>8e Arrondissement (Élysée / Madeleine)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 75001 à 75020 (750XX)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 750 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>75008 (Champs-Élysées), 75009 (Opéra)</t>
         </is>
       </c>
     </row>
@@ -588,17 +596,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18e Arrondissement (Montmartre)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>75018</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>e3-fr-par-18</t>
+          <t>18e Arrondissement (Montmartre / Goutte d'Or)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 75001 à 75020 (750XX)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 750 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>75018 (Montmartre), 75019 (Buttes-Chaumont)</t>
         </is>
       </c>
     </row>
@@ -620,17 +633,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2e Arrondissement (Presqu'île)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>69002</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>e4-fr-lyo-2</t>
+          <t>2e Arrondissement (Presqu'île / Bellecour)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 69001 à 69009 (6900X)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 6900 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69001 (Terreaux), 69002 (Bellecour)</t>
         </is>
       </c>
     </row>
@@ -652,17 +670,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5e Arrondissement (Vieux Lyon)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>69005</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>e5-fr-lyo-5</t>
+          <t>5e Arrondissement (Vieux Lyon / Fourvière)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 69001 à 69009 (6900X)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 6900 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>69005 (Vieux Lyon), 69004 (Croix-Rousse)</t>
         </is>
       </c>
     </row>
@@ -684,17 +707,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1er Arrondissement (Vieux-Port)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>13001</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>e6-fr-mar-1</t>
+          <t>1er Arrondissement (Vieux-Port / Noailles)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 13001 à 13016 (130XX)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 130 + N° d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13001 (Vieux-Port), 13006 (Castellane)</t>
         </is>
       </c>
     </row>
@@ -716,17 +744,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Centre-ville / Quinconces</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>e7-fr-bdx</t>
+          <t>Centre-ville / Quinconces / Chartrons</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 33000 à 33800 (33XXX)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 33 (Gironde) + découpage municipal</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33000 (Hypercentre), 33200 (Caudéran)</t>
         </is>
       </c>
     </row>
@@ -751,14 +784,19 @@
           <t>Pentagone / Centre Historique</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>e8-be-bru</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 1000 à 1210 (1XXX)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4 chiffres : 1XXX pour Bruxelles-Capitale</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1000 (Bruxelles-Ville), 1050 (Ixelles)</t>
         </is>
       </c>
     </row>
@@ -770,27 +808,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Belgique</t>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ixelles</t>
+          <t>Genève</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Flagey - Châtelain</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>e9-be-ixe</t>
+          <t>Les Pâquis / Rive Droite</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 1200 à 1211 (12XX)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4 chiffres : 12XX pour le canton de Genève</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1201 (Pâquis/Gare), 1204 (Vieille-Ville)</t>
         </is>
       </c>
     </row>
@@ -802,27 +845,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Suisse</t>
+          <t>Espagne</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Genève</t>
+          <t>Barcelone</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Les Pâquis</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>e10-ch-gen</t>
+          <t>Eixample / Gràcia</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 08001 à 08042 (080XX)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 08 (Province) + district postal</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>08007 (Eixample Dret), 08012 (Gràcia)</t>
         </is>
       </c>
     </row>
@@ -834,27 +882,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Espagne</t>
+          <t>Allemagne</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Barcelone</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Eixample</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>08007</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>e11-es-bar</t>
+          <t>Mitte / Tiergarten</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 10115 à 14199 (1XXXX)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : Zone postale 1 par secteur municipal</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10115 (Mitte Nord), 10117 (Mitte Sud)</t>
         </is>
       </c>
     </row>
@@ -866,91 +919,106 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Espagne</t>
+          <t>Royaume-Uni</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Malasaña</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>28004</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>e12-es-mad</t>
+          <t>Westminster / City of London</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Alphanumérique par Secteur</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Lettres cardinales (SW, EC, W) + Chiffres + District</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SW1A (Westminster), EC1A (City Nord), W1D (Soho)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Afrique</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Allemagne</t>
+          <t>Cameroun</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Douala</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mitte</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>10115</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>e13-de-ber</t>
+          <t>Douala 1er (Akwa / Bonanjo)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Boîte Postale / Agence (BP 1000 à 1500)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Mention 'BP' + 4 chiffres selon l'agence urbaine</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>BP 1024 (Akwa), BP 1010 (Bonanjo), BP 1015 (Bonapriso)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Afrique</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Royaume-Uni</t>
+          <t>Cameroun</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Yaoundé</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>SW1A 1AA</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>e14-uk-lon</t>
+          <t>Yaoundé 1er (Bastos / Omnisports)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Boîte Postale / Agence (BP 8000 à 8500)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Mention 'BP' + 4 chiffres selon le centre de tri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>BP 8001 (Bastos), BP 8012 (Omnisports)</t>
         </is>
       </c>
     </row>
@@ -962,27 +1030,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cameroun</t>
+          <t>Sénégal</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Akwa</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BP 1024</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>a1-cm-dla-1</t>
+          <t>Dakar-Plateau / Médina</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 10000 à 12500 (5 chiffres)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 10000 à 19999 pour la presqu'île</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10200 (Dakar-Plateau), 10500 (Almadies)</t>
         </is>
       </c>
     </row>
@@ -994,27 +1067,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cameroun</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Bonanjo</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>BP 1010</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>a2-cm-dla-2</t>
+          <t>Cocody / Deux-Plateaux</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Boîte Postale Communale (01 BP à 30 BP)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Numéro communal (ex: 01 BP) + 4 chiffres de bureau</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>01 BP 1200 (Cocody), 01 BP 1000 (Plateau)</t>
         </is>
       </c>
     </row>
@@ -1026,763 +1104,365 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cameroun</t>
+          <t>Maroc</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Bonapriso</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BP 1015</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>a3-cm-dla-3</t>
+          <t>Anfa / Maârif / Sidi Belyout</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 20000 à 20700 (5 chiffres)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 20XXX pour le Grand Casablanca</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20100 (Maârif), 20000 (Sidi Belyout)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Nord</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cameroun</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Yaoundé</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Bastos</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>BP 8001</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>a4-cm-yao-1</t>
+          <t>Le Plateau-Mont-Royal / Mile-End</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Alphanumérique H2X / H2W (ANA NAN)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>H (Grand Montréal) + Alternance Chiffre/Lettre : H#X #X#</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>H2W 1V8 (Plateau Ouest), H2T 2M5 (Mile End)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Nord</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cameroun</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Yaoundé</t>
+          <t>Montréal</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Omnisports</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>BP 8012</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>a5-cm-yao-2</t>
+          <t>Ville-Marie / Vieux-Montréal</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Alphanumérique H2Y / H3B / H3C (ANA NAN)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>H (Grand Montréal) + Alternance Chiffre/Lettre : H#X #X#</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>H2Y 1G5 (Vieux-Montréal), H3B 4G7 (Centre-ville)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Nord</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sénégal</t>
+          <t>États-Unis</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>10200</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>a6-sn-dak-1</t>
+          <t>Manhattan (SoHo / Greenwich Village)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Modèle ZIP Code 10001 à 10282 (100XX)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 100XX spécifique à l'île de Manhattan</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10012 (SoHo), 10014 (West Village)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Nord</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sénégal</t>
+          <t>États-Unis</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Almadies</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>a7-sn-dak-2</t>
+          <t>Brooklyn (Williamsburg / DUMBO)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Modèle ZIP Code 11201 à 11256 (112XX)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5 chiffres : 112XX spécifique aux quartiers de Brooklyn</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11211 (Williamsburg), 11201 (DUMBO)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Sud</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Brésil</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Cocody</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>01 BP 1200</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>a8-ci-abj-1</t>
+          <t>Jardins / Cerqueira César</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Modèle CEP 01000-000 à 05999-999 (014XX-XXX)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8 chiffres format CEP : 5 chiffres + tiret + 3 chiffres</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>01410-000 (Jardins), 01415-000 (Cerqueira César)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Amérique du Sud</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Argentine</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>01 BP 1000</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>a9-ci-abj-2</t>
+          <t>Palermo / Recoleta</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Modèle CPA Alphanumérique (C14XX / C10XX)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Lettre C (Capital Federal) + 4 chiffres d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>C1425 (Palermo), C1018 (Recoleta)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Asie</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Maroc</t>
+          <t>Japon</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Maârif</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>20100</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>a10-ma-cas</t>
+          <t>Shibuya-ku</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 150-0000 à 151-9999 (150-XXXX)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7 chiffres : 3 chiffres + tiret + 4 chiffres d'arrondissement</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>150-0001 (Jingumae), 150-0002 (Shibuya)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Afrique</t>
+          <t>Asie</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Maroc</t>
+          <t>Émirats Arabes Unis</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Marrakech</t>
+          <t>Dubaï</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Guéliz</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>a11-ma-rak</t>
+          <t>Downtown Dubai / Business Bay</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Modèle Système Makani / P.O. Box Sectoriel</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Pas de code postal individuel : Makani (10 chiffres) ou P.O. Box</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Makani 30032 95320 (Burj Khalifa), P.O. Box 11111</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Amérique du Nord</t>
+          <t>Océanie</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australie</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>H2W 1V8</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>na1-ca-mtl-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Nord</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Montréal</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Vieux-Montréal</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>H2Y 1G5</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>na2-ca-mtl-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Nord</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Québec</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Vieux-Québec</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>G1R 4P5</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>na3-ca-que</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Nord</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>États-Unis</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Manhattan / SoHo</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>na4-us-nyc-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Nord</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>États-Unis</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Brooklyn / Williamsburg</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>11211</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>na5-us-nyc-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Nord</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>États-Unis</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Mission District</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>94110</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>na6-us-sfo</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Sud</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Brésil</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Jardins</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>01410-000</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>sa1-br-sao</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Sud</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Brésil</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Copacabana</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>22070-001</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>sa2-br-rio</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Amérique du Sud</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Argentine</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>C1425</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>sa3-ar-bue</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Asie</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Japon</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Shibuya</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>150-0002</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>as1-jp-tyo-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Asie</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Japon</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Shinjuku</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>160-0022</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>as2-jp-tyo-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Asie</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Singapour</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Singapour</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Marina Bay</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>018956</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>as3-sg-sin</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Asie</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Émirats Arabes Unis</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Dubaï</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Downtown Dubai</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>PO 11111</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>as4-ae-dxb</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Océanie</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Australie</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>The Rocks</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>oc1-au-syd</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Océanie</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Australie</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Carlton</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>oc2-au-mel</t>
+          <t>Sydney CBD / The Rocks / Haymarket</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Modèle 2000 à 2010 (2XXX)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>4 chiffres : Préfixe 2 (NSW) + tranche 2000-2010 centre</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2000 (CBD/The Rocks), 2010 (Surry Hills)</t>
         </is>
       </c>
     </row>
@@ -1797,382 +1477,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="115" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Fichier Analysé</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Type d'Élément</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Action Menée</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Statut Après Nettoyage</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pays / Zone</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Format Standard</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Description de la Structure</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Exemple de Quartier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>package.json</t>
+          <t>France (Paris, Lyon, Marseille)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Dépendance npm</t>
+          <t>5 chiffres (ex: 750XX, 6900X, 130XX)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Suppression du package @supabase/supabase-js</t>
+          <t>Code département (2 chiffres) + 0 + numéro de l'arrondissement</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Désinstallé</t>
+          <t>Paris 8e : 75008 / Lyon 2e : 69002</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>src/lib/supabase.ts</t>
+          <t>Belgique</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Client API / SDK</t>
+          <t>4 chiffres (ex: 1XXX)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Suppression intégrale du fichier client Supabase</t>
+          <t>Le premier chiffre désigne la région de tri (1 = Bruxelles)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Fichier Supprimé</t>
+          <t>Bruxelles-Ville : 1000 / Ixelles : 1050</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>src/lib/geo-storage.ts</t>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Service de Stockage</t>
+          <t>4 chiffres (ex: 12XX)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Retrait de l'import Supabase et passage au stockage local persistant pur</t>
+          <t>Attribution géographique par cantons et secteurs postaux</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100% Autonome</t>
+          <t>Genève Pâquis : 1201 / Plainpalais : 1205</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>src/components/Header.tsx</t>
+          <t>Royaume-Uni</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Composant UI</t>
+          <t>Alphanumérique (ex: SW1A, EC1A)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Remplacement du badge Supabase par le badge Base Locale Autonome et bouton Excel</t>
+          <t>Code zone cardinale + numéro de district + unité de livraison</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Interface Épurée</t>
+          <t>Londres Westminster : SW1A 1AA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>src/app/layout.tsx</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Métadonnées Next.js</t>
+          <t>Alphanumérique A1A 1A1 (ex: H2W 1V8)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Suppression de la mention Supabase dans le titre de l'application</t>
+          <t>Premier caractère = province/région urbaine (H = Montréal), suivi de l'alternance lettre/chiffre</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nettoyé</t>
+          <t>Plateau-Mont-Royal : H2W 1V8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>src/app/page.tsx</t>
+          <t>États-Unis</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Page Principale</t>
+          <t>ZIP Code 5 chiffres (ex: 100XX, 112XX)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Retrait des vérifications de connexion cloud et mentions Supabase</t>
+          <t>Premier chiffre = région, deux suivants = centre de tri, deux derniers = bureau postal</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Nettoyé</t>
+          <t>New York Manhattan : 10012 / Brooklyn : 11211</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>schema.sql</t>
+          <t>Afrique Francophone (Cameroun, CI)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Schéma de Base de Données</t>
+          <t>Boîtes Postales (BP) ou Code Commune</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Conversion en script SQL universel (PostgreSQL, MySQL, SQLite) sans dépendances Supabase</t>
+          <t>Distribution en boîtes postales sectorielles ou agences de rattachement communal</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Universel</t>
+          <t>Douala Akwa : BP 1024 / Abidjan Cocody : 01 BP 1200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>lancer-application.bat</t>
+          <t>Brésil</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Script de Lancement</t>
+          <t>CEP 8 chiffres (ex: 01410-000)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Mise à jour du script pour exécution locale directe sans service externe</t>
+          <t>Région (1 chiffre), sous-région (1), secteur (1), sous-secteur (1), diviseur (1) et suffixe de distribution (3)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Optimisé</t>
+          <t>São Paulo Jardins : 01410-000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Comment ca marche.txt</t>
+          <t>Japon</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Documentation utilisateur</t>
+          <t>7 chiffres (ex: 150-0002)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Suppression des étapes Supabase et documentation du mode autonome</t>
+          <t>3 chiffres régionaux suivis d'un tiret et de 4 chiffres d'arrondissement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Mis à jour</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>.env.example</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Variables d'environnement</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Suppression des clés d'API distantes NEXT_PUBLIC_SUPABASE_*</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Nettoyé</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>README.md</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Documentation du Dépôt</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Réécriture complète de la documentation pour refléter le mode local autonome</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Mis à jour</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Valeur</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total des localisations répertoriées</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Nombre de continents uniques</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Nombre de pays représentés</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Nombre de métropoles et villes</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Architecture hiérarchique</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Continent &gt; Pays &gt; Ville &gt; Quartier &gt; Code Postal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Mode de fonctionnement</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Local autonome avec persistance navigateur</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Compatibilité d'exportation</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Excel (.xlsx), CSV (UTF-8 avec BOM), JSON</t>
+          <t>Tokyo Shibuya : 150-0002</t>
         </is>
       </c>
     </row>
